--- a/DATA/INPUT/phase7_period_assignments.xlsx
+++ b/DATA/INPUT/phase7_period_assignments.xlsx
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">

--- a/DATA/INPUT/phase7_period_assignments.xlsx
+++ b/DATA/INPUT/phase7_period_assignments.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"departments": ["CSE", "DSAI", "ECE"], "section_groups": {"CSE": {"A": 1, "B": 1}, "DSAI": {"A": 2}, "ECE": {"A": 2}}, "sections_by_dept": {"CSE": ["A", "B"], "DSAI": ["A"], "ECE": ["A"]}, "students_per_section": 85}</t>
+          <t>{"departments": ["CSE", "DSAI", "ECE", "AIC"], "section_groups": {"AIC": {"A": 3}, "CSE": {"A": 1, "B": 1}, "DSAI": {"A": 2}, "ECE": {"A": 2}}, "sections_by_dept": {"AIC": ["A"], "CSE": ["A", "B"], "DSAI": ["A"], "ECE": ["A"]}, "students_per_section": 85}</t>
         </is>
       </c>
     </row>
